--- a/Result/profitability/1730.xlsx
+++ b/Result/profitability/1730.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.3</v>
       </c>
       <c r="M2" t="n">
-        <v>1.0475</v>
+        <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>49.535</v>
+        <v>49.975</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -783,7 +783,7 @@
         <v>0.93</v>
       </c>
       <c r="N3" t="n">
-        <v>49.2325</v>
+        <v>49.47875000000001</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.08</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8125</v>
+        <v>0.7712499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>48.755</v>
+        <v>48.8525</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.16</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6637500000000001</v>
+        <v>0.6812499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>47.92375</v>
+        <v>47.97125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.22</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5812499999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>47.5425</v>
+        <v>47.3825</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.39</v>
       </c>
       <c r="M7" t="n">
-        <v>0.48125</v>
+        <v>0.47375</v>
       </c>
       <c r="N7" t="n">
-        <v>46.9325</v>
+        <v>46.8675</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.36</v>
       </c>
       <c r="M8" t="n">
-        <v>0.39125</v>
+        <v>0.33375</v>
       </c>
       <c r="N8" t="n">
-        <v>46.73625</v>
+        <v>46.76125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>0.27625</v>
       </c>
       <c r="N10" t="n">
-        <v>46.83624999999999</v>
+        <v>46.83625</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>0.29375</v>
       </c>
       <c r="N11" t="n">
-        <v>46.99875</v>
+        <v>46.99874999999999</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>0.3475</v>
       </c>
       <c r="N12" t="n">
-        <v>47.1975</v>
+        <v>47.19750000000001</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1730</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>606</v>
+      </c>
+      <c r="D75" t="n">
+        <v>298</v>
+      </c>
+      <c r="E75" t="n">
+        <v>308</v>
+      </c>
+      <c r="F75" t="n">
+        <v>50.84</v>
+      </c>
+      <c r="G75" t="n">
+        <v>86</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>14.25%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>8</v>
+      </c>
+      <c r="J75" t="n">
+        <v>95</v>
+      </c>
+      <c r="K75" t="n">
+        <v>65</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.1375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>50.20875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.3108108108108107</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.2000000000000028</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.003949447077409296</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.1590909090909092</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.3800000000000026</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.007530717399920839</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
